--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="467">
   <si>
     <t>ID</t>
   </si>
@@ -410,6 +410,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -818,6 +823,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -859,6 +869,9 @@
     <t>寒暄一阵后，靠在门边休息的克拉克这才注意到这位出来的“同伴”，他那双还蒙着麻药雾气的眼睛扫过索菲亚沾着尘土和血污的外套，又抬眼看向你，眼神里带着明显的疑惑。</t>
   </si>
   <si>
+    <t>bgfade(sntzm_final(4)_28,1)</t>
+  </si>
+  <si>
     <t>88</t>
   </si>
   <si>
@@ -962,6 +975,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadein(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -5639,7 +5657,7 @@
         <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="L77" t="s">
         <v>24</v>
@@ -5647,7 +5665,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
         <v>84</v>
@@ -5665,7 +5683,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5680,12 +5698,12 @@
         <v>157</v>
       </c>
       <c r="L78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B79" t="s">
         <v>109</v>
@@ -5703,7 +5721,7 @@
         <v>171</v>
       </c>
       <c r="G79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5718,12 +5736,12 @@
         <v>192</v>
       </c>
       <c r="L79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5741,7 +5759,7 @@
         <v>171</v>
       </c>
       <c r="G80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5761,7 +5779,7 @@
     </row>
     <row r="81" ht="70.5" spans="1:12">
       <c r="A81" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
         <v>109</v>
@@ -5779,7 +5797,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5794,12 +5812,12 @@
         <v>157</v>
       </c>
       <c r="L81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5817,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5832,12 +5850,12 @@
         <v>161</v>
       </c>
       <c r="L82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s">
         <v>84</v>
@@ -5855,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5870,12 +5888,12 @@
         <v>157</v>
       </c>
       <c r="L83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" ht="27" spans="1:12">
       <c r="A84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5893,7 +5911,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5910,7 +5928,7 @@
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B85" t="s">
         <v>84</v>
@@ -5928,7 +5946,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5943,12 +5961,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
@@ -5963,10 +5981,10 @@
         <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -5981,12 +5999,12 @@
         <v>192</v>
       </c>
       <c r="L86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="87" ht="55.5" spans="1:12">
       <c r="A87" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B87" t="s">
         <v>26</v>
@@ -6001,10 +6019,10 @@
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6019,12 +6037,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6039,10 +6057,10 @@
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6057,12 +6075,12 @@
         <v>196</v>
       </c>
       <c r="L88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89" ht="54" spans="1:12">
       <c r="A89" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
@@ -6071,7 +6089,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6080,7 +6098,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6092,10 +6110,10 @@
         <v>15</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L89" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -6116,47 +6134,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -6164,7 +6182,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -6172,7 +6190,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -6180,58 +6198,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -6253,616 +6271,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C15" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C17" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B18" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C18" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D18" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F18" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B19" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D20" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F20" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C21" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D21" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F21" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C22" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D22" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E22" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C23" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B24" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D24" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E24" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B25" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C25" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E25" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B26" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C26" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D26" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E26" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F26" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B27" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C27" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B28" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C28" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D28" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D29" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E29" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B30" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C30" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E30" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F30" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B31" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C31" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D31" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(6).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局3" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="475">
   <si>
     <t>ID</t>
   </si>
@@ -201,6 +201,12 @@
     <t>控制台的屏幕骤然闪烁起刺眼的蓝光，整间舱室都被这突如其来的光亮填满，原本贴在墙壁上流动的阴影一下子被冲得四散开来。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music17)</t>
+  </si>
+  <si>
     <t>27</t>
   </si>
   <si>
@@ -348,38 +354,7 @@
     <t>bgfade(sntzm_final(6)_44,1)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>源类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">=type:txt_pb; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=18</t>
-    </r>
+    <t>源类型=type:txt_pb; 层级=18</t>
   </si>
   <si>
     <t>53</t>
@@ -495,7 +470,7 @@
     <t>54</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=21</t>
+    <t>源类型=type:txt_David; 层级=21</t>
   </si>
   <si>
     <t>55</t>
@@ -612,13 +587,19 @@
     <t>源类型=type:txt_David; 层级=32</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=33</t>
+  </si>
+  <si>
     <t>67</t>
   </si>
   <si>
     <t>他从电椅上挣扎起身，虽因久卧昏迷而双腿僵硬，但心中怒火提供的热度，足以支撑他站稳脚跟。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=33</t>
+    <t>源类型=type:txt_pb; 层级=34</t>
   </si>
   <si>
     <t>68</t>
@@ -630,7 +611,7 @@
     <t>bgfade(sntzm_final(4)_38,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=34</t>
+    <t>源类型=type:txt_pb; 层级=35</t>
   </si>
   <si>
     <t>69</t>
@@ -639,7 +620,7 @@
     <t>他不见了。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=35</t>
+    <t>源类型=type:txt_Clark; 层级=36</t>
   </si>
   <si>
     <t>70</t>
@@ -648,7 +629,7 @@
     <t>他眉头拧起，把手电微微朝向隔间外侧打去，但那里没有脚印、没有血迹，更没有留下半分残存的体温，就好像亚波伦这个人，从始至终都只是你们眼前凭空冒出来的一抹幻影。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=36</t>
+    <t>源类型=type:txt_pb; 层级=37</t>
   </si>
   <si>
     <t>71</t>
@@ -657,7 +638,7 @@
     <t>而且没有从来没有离开过这个隔间。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=37</t>
+    <t>源类型=type:txt_Clark; 层级=38</t>
   </si>
   <si>
     <t>72</t>
@@ -669,7 +650,7 @@
     <t>parallel(charfadeout(L,1);charfadein(R,1))</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=38</t>
+    <t>源类型=type:txt_David; 层级=39</t>
   </si>
   <si>
     <t>73</t>
@@ -681,7 +662,7 @@
     <t>charfadeout(R,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=39</t>
+    <t>源类型=type:txt_pb; 层级=40</t>
   </si>
   <si>
     <t>74</t>
@@ -690,7 +671,10 @@
     <t>好了，都已经过去了。既然不知道那家伙去了哪里，那我想我们还是早点离开这鬼地方比较好。如果亚波伦通过某种障眼法活了下来，那他随时都有可能对我们构成新的威胁。</t>
   </si>
   <si>
-    <t>源类型=type:txt_You; 层级=40</t>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=41</t>
   </si>
   <si>
     <t>75</t>
@@ -699,7 +683,7 @@
     <t>大卫微微垂下头，似乎是默认了你的说法。一旁的克拉克也不再多言，扛起他的肩膀就要往隔间外走。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=41</t>
+    <t>源类型=type:txt_pb; 层级=42</t>
   </si>
   <si>
     <t>76</t>
@@ -708,7 +692,7 @@
     <t>刚刚经历过一场惊心动魄的剧变，这间密闭冰冷的手术室里到处都残留着死亡的气息，无论先前各自经历了什么，“离开这个该死的鬼地方”已经成为了你们此刻心照不宣的共同选择。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=42</t>
+    <t>源类型=type:txt_pb; 层级=43</t>
   </si>
   <si>
     <t>77</t>
@@ -717,7 +701,7 @@
     <t>你抬手按了按突突直跳的太阳穴，正准备转身带路，</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=43</t>
+    <t>源类型=type:txt_pb; 层级=44</t>
   </si>
   <si>
     <t>78</t>
@@ -726,10 +710,13 @@
     <t>可就在大卫前脚踏出隔间的那一刻，整间手术室的灯光猛地一暗，原本还平稳运行的供电系统突然中断，应急灯在三秒的延迟后才亮起幽幽的暗红。</t>
   </si>
   <si>
+    <t>18 enhanced_APPLE</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_final(3)_110,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=44</t>
+    <t>源类型=type:txt_pb; 层级=45</t>
   </si>
   <si>
     <t>79</t>
@@ -738,7 +725,7 @@
     <t>那家伙果然还留了后手，我就知道他不会这么容易放我们离开！</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=45</t>
+    <t>源类型=type:txt_David; 层级=46</t>
   </si>
   <si>
     <t>80</t>
@@ -750,7 +737,7 @@
     <t>charfadeout(L,1)&amp;playsfx(RubbleCrash)&amp;parallel(bgfade(sntzm_final(6)_80,1);shake(screen,10,0.5))</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=46</t>
+    <t>源类型=type:txt_pb; 层级=47</t>
   </si>
   <si>
     <t>81</t>
@@ -759,7 +746,7 @@
     <t>地震？这种时候......</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=47</t>
+    <t>源类型=type:txt_Clark; 层级=48</t>
   </si>
   <si>
     <t>82</t>
@@ -768,7 +755,7 @@
     <t>不，不是地震。这里的整个空间都在崩坏......</t>
   </si>
   <si>
-    <t>源类型=type:txt_You; 层级=48</t>
+    <t>源类型=type:txt_You; 层级=49</t>
   </si>
   <si>
     <t>83</t>
@@ -777,7 +764,7 @@
     <t>你伸手扶着裂开的墙沿稳住重心，指尖触碰到的砖石正在快速化为细碎的沙砾，脚下的地面由坚实渐渐变为蓬松柔软的质地，仿佛站在一艘被水浸湿的纸船上，整艘船正以惊人的速度起泡发软。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=49</t>
+    <t>源类型=type:txt_pb; 层级=50</t>
   </si>
   <si>
     <t>84</t>
@@ -786,7 +773,7 @@
     <t>顾不得深究这种现象发生的原因，你们立刻以最快速度朝着门口的方向跑去。不管起因如何，此刻能带你们逃离这崩毁之地的，并非纷乱的思绪或嘈杂的言语，而是三条尚能奔跑的双腿。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=50</t>
+    <t>源类型=type:txt_pb; 层级=51</t>
   </si>
   <si>
     <t>85</t>
@@ -795,13 +782,13 @@
     <t>暗红色的应急灯光在剧烈的摇晃中不停晃过你们绷紧的脸，墙壁坍落扬起的灰尘呛得人难以呼吸，墙皮下的霉味混杂着一股甜香的药物气息充斥着室内的空气，让你在奔跑的过程中不由得捂住口鼻。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=51</t>
+    <t>源类型=type:txt_pb; 层级=52</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
-    <t>源类型=type:exeBC; 层级=52</t>
+    <t>源类型=type:exeBC; 层级=53</t>
   </si>
   <si>
     <t>86</t>
@@ -813,7 +800,7 @@
     <t>bgfade(sntzm_final(6)_86,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=53; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=54; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>87</t>
@@ -848,7 +835,7 @@
     </r>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=54; gotomainline=盖亚之心（上）_3</t>
+    <t>源类型=type:txt_pb; 层级=55; gotomainline=盖亚之心（上）_3</t>
   </si>
   <si>
     <t>101</t>
@@ -860,7 +847,39 @@
     <t>bgfade(sntzm_final(6)_86,1)&amp;jump(87)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=53; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=87</t>
+    <t>源类型=type:txt_pb; 层级=54; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=87</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 92)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=34; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"相信索菲亚","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=终局（下）_92</t>
   </si>
   <si>
     <t>56</t>
@@ -1018,7 +1037,7 @@
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/9/3 16:03:34</t>
+    <t>2026/9/24 15:40:36</t>
   </si>
   <si>
     <t>输出节点数</t>
@@ -1042,25 +1061,22 @@
     <t>说话人映射数</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>规则</t>
   </si>
   <si>
     <t>datatype=type:txt_* -&gt; 按 节点类型转中文.xlsx 的 Type/Name 映射生成 Speaker</t>
   </si>
   <si>
-    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(分支首句ID))</t>
+    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(选项入口ID))</t>
   </si>
   <si>
     <t>selectBC 直接子节点作为选项入口时，不再把选项文字写入 Text</t>
   </si>
   <si>
-    <t>选项入口 Note 除源类型/层级外，其余字段追加到分支首句 Note</t>
-  </si>
-  <si>
-    <t>gotomainline 数字 -&gt; jump(ID)；非数字 -&gt; loadScript(文件名, 1)</t>
+    <t>选项入口保留自身 tag 等 Note 字段；Command 优先使用 gotomainline，否则 jump 到第一个子节点</t>
+  </si>
+  <si>
+    <t>gotomainline 数字 -&gt; jump(ID)；文件名_数字 -&gt; loadScript(文件名, 数字)；其他非数字 -&gt; loadScript(文件名, 1)</t>
   </si>
   <si>
     <t>pic -&gt; Background；music -&gt; BGM；无语音时第一行 Voice=false</t>
@@ -1583,11 +1599,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1740,6 +1751,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2048,28 +2064,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2078,130 +2097,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2739,7 +2752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2897,6 +2910,9 @@
       <c r="J4" t="s">
         <v>15</v>
       </c>
+      <c r="K4" t="s">
+        <v>15</v>
+      </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
@@ -3198,6 +3214,9 @@
       <c r="J12" t="s">
         <v>15</v>
       </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
       <c r="L12" t="s">
         <v>49</v>
       </c>
@@ -3240,7 +3259,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" ht="40.5" spans="1:12">
+    <row r="14" ht="60" spans="1:12">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -3266,10 +3285,13 @@
         <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>56</v>
       </c>
       <c r="L14" t="s">
         <v>24</v>
@@ -3277,7 +3299,7 @@
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3295,7 +3317,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3307,15 +3329,15 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="27" spans="1:12">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3333,7 +3355,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3353,7 +3375,7 @@
     </row>
     <row r="17" ht="54" spans="1:12">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3371,7 +3393,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3386,12 +3408,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="54" spans="1:12">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3409,7 +3431,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3429,7 +3451,7 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -3447,7 +3469,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3459,7 +3481,7 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
         <v>40</v>
@@ -3467,7 +3489,7 @@
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3485,7 +3507,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3500,12 +3522,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="42" spans="1:12">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3523,7 +3545,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3543,7 +3565,7 @@
     </row>
     <row r="22" ht="42" spans="1:12">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3561,7 +3583,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3581,7 +3603,7 @@
     </row>
     <row r="23" ht="55.5" spans="1:12">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3599,7 +3621,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3614,12 +3636,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:12">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3637,7 +3659,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3649,18 +3671,18 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3675,7 +3697,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3690,12 +3712,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3728,12 +3750,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" ht="90" spans="1:12">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3751,7 +3773,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3766,12 +3788,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" ht="42" spans="1:12">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3789,7 +3811,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3804,12 +3826,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3827,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3842,12 +3864,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3865,7 +3887,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3880,12 +3902,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" ht="55.5" spans="1:12">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3903,7 +3925,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3915,15 +3937,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>103</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="L31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32" ht="40.5" spans="1:12">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3941,7 +3963,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3956,15 +3978,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3979,7 +4001,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3994,12 +4016,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4017,7 +4039,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4028,16 +4050,16 @@
       <c r="J34" t="s">
         <v>15</v>
       </c>
-      <c r="K34" s="3" t="s">
-        <v>114</v>
+      <c r="K34" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="L34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" ht="90" spans="1:12">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4055,7 +4077,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4070,12 +4092,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" ht="67.5" spans="1:12">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4093,7 +4115,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4108,15 +4130,15 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
@@ -4131,7 +4153,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4146,12 +4168,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4169,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4184,15 +4206,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B39" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4207,7 +4229,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4222,12 +4244,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" ht="42" spans="1:12">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4245,7 +4267,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4257,15 +4279,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" ht="40.5" spans="1:12">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4283,7 +4305,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4298,15 +4320,15 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4321,7 +4343,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4336,12 +4358,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4359,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4374,12 +4396,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4397,7 +4419,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4409,18 +4431,18 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L44" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -4435,7 +4457,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4450,12 +4472,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" ht="27" spans="1:12">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4473,7 +4495,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4488,15 +4510,15 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -4511,7 +4533,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4526,12 +4548,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" ht="55.5" spans="1:12">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4549,7 +4571,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4560,22 +4582,25 @@
       <c r="J48" t="s">
         <v>15</v>
       </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
       <c r="L48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4584,7 +4609,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4596,24 +4621,24 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4622,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4634,15 +4659,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4660,7 +4685,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4675,15 +4700,15 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -4698,7 +4723,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4710,24 +4735,24 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L52" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" ht="28.5" spans="1:12">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4736,7 +4761,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4748,15 +4773,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="54" ht="27" spans="1:12">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4764,9 +4789,6 @@
       <c r="C54" t="s">
         <v>14</v>
       </c>
-      <c r="D54" t="s">
-        <v>171</v>
-      </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
@@ -4774,7 +4796,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4785,16 +4807,13 @@
       <c r="J54" t="s">
         <v>15</v>
       </c>
-      <c r="K54" t="s">
-        <v>161</v>
-      </c>
       <c r="L54" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="55" ht="40.5" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4803,7 +4822,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4812,7 +4831,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4824,24 +4843,24 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
         <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4862,62 +4881,62 @@
         <v>15</v>
       </c>
       <c r="K56" t="s">
+        <v>183</v>
+      </c>
+      <c r="L56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" t="s">
         <v>157</v>
       </c>
-      <c r="L56" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" ht="54" spans="1:12">
-      <c r="A57" t="s">
-        <v>184</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" ht="54" spans="1:12">
+      <c r="A58" t="s">
+        <v>188</v>
+      </c>
+      <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>185</v>
-      </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
-        <v>161</v>
-      </c>
-      <c r="L57" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" t="s">
-        <v>187</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
       <c r="C58" t="s">
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4926,7 +4945,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4938,33 +4957,33 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
         <v>157</v>
       </c>
-      <c r="L58" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" ht="55.5" spans="1:12">
-      <c r="A59" t="s">
-        <v>190</v>
-      </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>155</v>
-      </c>
       <c r="E59" t="s">
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4976,27 +4995,30 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="L59" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="60" ht="40.5" spans="1:12">
+    <row r="60" ht="55.5" spans="1:12">
       <c r="A60" t="s">
         <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
+      <c r="D60" t="s">
+        <v>157</v>
+      </c>
       <c r="E60" t="s">
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G60" t="s">
         <v>195</v>
@@ -5017,12 +5039,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="61" ht="54" spans="1:12">
+    <row r="61" ht="40.5" spans="1:12">
       <c r="A61" t="s">
         <v>198</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
@@ -5034,7 +5056,7 @@
         <v>15</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="G61" t="s">
         <v>199</v>
@@ -5049,18 +5071,18 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="L61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62" ht="40.5" spans="1:12">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5075,13 +5097,13 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
+        <v>204</v>
       </c>
       <c r="J62" t="s">
         <v>15</v>
@@ -5090,12 +5112,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" ht="55.5" spans="1:12">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5113,7 +5135,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5128,12 +5150,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64" ht="27" spans="1:12">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64" ht="55.5" spans="1:12">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5151,7 +5173,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5166,12 +5188,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="65" ht="40.5" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" ht="27" spans="1:12">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5189,7 +5211,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5201,24 +5223,24 @@
         <v>15</v>
       </c>
       <c r="K65" t="s">
-        <v>212</v>
+        <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="66" ht="27" spans="1:12">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5227,74 +5249,74 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="J66" t="s">
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L66" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" ht="45" spans="1:12">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="67" ht="27" spans="1:12">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B67" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>221</v>
+      </c>
+      <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>159</v>
+      </c>
+      <c r="L67" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="68" ht="45" spans="1:12">
+      <c r="A68" t="s">
+        <v>223</v>
+      </c>
+      <c r="B68" t="s">
         <v>13</v>
       </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>171</v>
-      </c>
-      <c r="E67" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" t="s">
-        <v>218</v>
-      </c>
-      <c r="H67" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" t="s">
-        <v>219</v>
-      </c>
-      <c r="L67" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
-      <c r="A68" t="s">
-        <v>221</v>
-      </c>
-      <c r="B68" t="s">
-        <v>84</v>
-      </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5303,7 +5325,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5315,24 +5337,24 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="L68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
         <v>15</v>
@@ -5341,7 +5363,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5353,24 +5375,24 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L69" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="70" ht="54" spans="1:12">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
@@ -5379,7 +5401,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5391,15 +5413,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="L70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" ht="54" spans="1:12">
       <c r="A71" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5417,7 +5439,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5432,12 +5454,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" ht="54" spans="1:12">
       <c r="A72" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5455,7 +5477,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5470,12 +5492,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5493,7 +5515,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>240</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5508,12 +5530,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="74" ht="90" spans="1:12">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5531,7 +5553,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>239</v>
+        <v>15</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5543,15 +5565,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>240</v>
+        <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="75" ht="54" spans="1:12">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="75" ht="90" spans="1:12">
       <c r="A75" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5569,7 +5591,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5580,16 +5602,16 @@
       <c r="J75" t="s">
         <v>15</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>244</v>
+      <c r="K75" t="s">
+        <v>246</v>
       </c>
       <c r="L75" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="76" ht="150" spans="1:12">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5607,7 +5629,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5618,16 +5640,16 @@
       <c r="J76" t="s">
         <v>15</v>
       </c>
-      <c r="K76" t="s">
-        <v>248</v>
+      <c r="K76" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="L76" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="77" ht="55.5" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" ht="150" spans="1:12">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5645,7 +5667,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5657,109 +5679,109 @@
         <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L77" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="78" ht="105" spans="1:12">
+      <c r="A78" t="s">
+        <v>256</v>
+      </c>
+      <c r="B78" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s">
+        <v>179</v>
+      </c>
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" ht="55.5" spans="1:12">
+      <c r="A79" t="s">
+        <v>259</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>260</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>261</v>
+      </c>
+      <c r="L79" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" t="s">
-        <v>253</v>
-      </c>
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" t="s">
-        <v>155</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" t="s">
-        <v>254</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>157</v>
-      </c>
-      <c r="L78" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" t="s">
-        <v>256</v>
-      </c>
-      <c r="B79" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>155</v>
-      </c>
-      <c r="E79" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" t="s">
-        <v>171</v>
-      </c>
-      <c r="G79" t="s">
-        <v>257</v>
-      </c>
-      <c r="H79" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" t="s">
-        <v>15</v>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
-      </c>
-      <c r="K79" t="s">
-        <v>192</v>
-      </c>
-      <c r="L79" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5771,53 +5793,53 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
+        <v>159</v>
+      </c>
+      <c r="L80" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>265</v>
+      </c>
+      <c r="B81" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>157</v>
+      </c>
+      <c r="E81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" t="s">
+        <v>173</v>
+      </c>
+      <c r="G81" t="s">
+        <v>266</v>
+      </c>
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
         <v>196</v>
       </c>
-      <c r="L80" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" ht="70.5" spans="1:12">
-      <c r="A81" t="s">
-        <v>261</v>
-      </c>
-      <c r="B81" t="s">
-        <v>109</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>171</v>
-      </c>
-      <c r="E81" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" t="s">
-        <v>262</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" t="s">
-        <v>157</v>
-      </c>
       <c r="L81" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="82" ht="27" spans="1:12">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5826,16 +5848,16 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="G82" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5847,24 +5869,24 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="L82" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="83" ht="42" spans="1:12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" ht="70.5" spans="1:12">
       <c r="A83" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E83" t="s">
         <v>15</v>
@@ -5873,7 +5895,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5885,15 +5907,15 @@
         <v>15</v>
       </c>
       <c r="K83" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L83" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="84" ht="27" spans="1:12">
       <c r="A84" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5902,7 +5924,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -5911,7 +5933,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5922,107 +5944,107 @@
       <c r="J84" t="s">
         <v>15</v>
       </c>
+      <c r="K84" t="s">
+        <v>163</v>
+      </c>
       <c r="L84" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="85" ht="42" spans="1:12">
+      <c r="A85" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>157</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>277</v>
+      </c>
+      <c r="H85" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>159</v>
+      </c>
+      <c r="L85" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" ht="27" spans="1:12">
+      <c r="A86" t="s">
+        <v>279</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" t="s">
+        <v>157</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s">
+        <v>280</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>15</v>
+      </c>
+      <c r="L86" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="85" ht="27" spans="1:12">
-      <c r="A85" t="s">
-        <v>272</v>
-      </c>
-      <c r="B85" t="s">
-        <v>84</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>155</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" t="s">
-        <v>273</v>
-      </c>
-      <c r="H85" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" t="s">
-        <v>15</v>
-      </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
-      <c r="L85" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="86" ht="40.5" spans="1:12">
-      <c r="A86" t="s">
-        <v>275</v>
-      </c>
-      <c r="B86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>155</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>276</v>
-      </c>
-      <c r="G86" t="s">
-        <v>277</v>
-      </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" t="s">
-        <v>15</v>
-      </c>
-      <c r="K86" t="s">
-        <v>192</v>
-      </c>
-      <c r="L86" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="87" ht="55.5" spans="1:12">
+    <row r="87" ht="27" spans="1:12">
       <c r="A87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6037,30 +6059,30 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G88" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6075,12 +6097,12 @@
         <v>196</v>
       </c>
       <c r="L88" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="89" ht="54" spans="1:12">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="89" ht="55.5" spans="1:12">
       <c r="A89" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
@@ -6089,16 +6111,16 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="G89" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6109,11 +6131,87 @@
       <c r="J89" t="s">
         <v>15</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>287</v>
+      <c r="K89" t="s">
+        <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>288</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="90" ht="40.5" spans="1:12">
+      <c r="A90" t="s">
+        <v>291</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" t="s">
+        <v>285</v>
+      </c>
+      <c r="G90" t="s">
+        <v>292</v>
+      </c>
+      <c r="H90" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>200</v>
+      </c>
+      <c r="L90" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="91" ht="54" spans="1:12">
+      <c r="A91" t="s">
+        <v>294</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" t="s">
+        <v>285</v>
+      </c>
+      <c r="E91" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" t="s">
+        <v>15</v>
+      </c>
+      <c r="G91" t="s">
+        <v>295</v>
+      </c>
+      <c r="H91" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" t="s">
+        <v>15</v>
+      </c>
+      <c r="J91" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="L91" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -6134,47 +6232,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -6182,74 +6280,74 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B10" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B12" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" ht="58.5" spans="1:2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" ht="88.5" spans="1:2">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" ht="60" spans="1:2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B14" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B15" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6271,616 +6369,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C2" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E2" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C3" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D3" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E3" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F3" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="F4" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D5" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E5" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F5" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F6" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C7" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D7" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="E7" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="F7" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B8" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="E8" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F8" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E9" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F9" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B10" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C10" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D10" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E10" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F10" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C11" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="D11" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E11" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="F11" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B12" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C12" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D12" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E12" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F12" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B13" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C13" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="D13" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E13" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F13" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B14" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C14" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="D14" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="E14" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="F14" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B15" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D15" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="E15" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F15" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B16" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C16" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D16" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E16" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F16" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B17" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C17" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D17" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E17" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F17" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B18" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C18" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D18" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="E18" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F18" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B19" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C19" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D19" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E19" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F19" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B20" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C20" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D20" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E20" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F20" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B21" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C21" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D21" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="E21" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F21" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B22" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="D22" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F22" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C23" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D23" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="E23" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="F23" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B24" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C24" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D24" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E24" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F24" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B25" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C25" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="D25" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="E25" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F25" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B26" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C26" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="D26" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="E26" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="F26" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B27" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C27" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D27" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E27" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F27" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B28" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C28" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="D28" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E28" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F28" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B29" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C29" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D29" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E29" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="F29" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B30" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C30" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D30" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E30" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F30" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B31" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C31" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D31" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
